--- a/docs/qa/upload-templates/production_orders_upload_template.xlsx
+++ b/docs/qa/upload-templates/production_orders_upload_template.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,6 +483,21 @@
           <t>priority</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>work_centre_code</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>customer_code</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sales_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -518,6 +533,21 @@
           <t>high</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>WC-WND</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>CUST-EE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>SO-2026-0290</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -553,6 +583,21 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>WC-WND</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>CUST-SEC</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>SO-2026-0289</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -588,6 +633,13 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>WC-ASM</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
